--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -46,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,13 +57,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">

--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -739,8 +739,8 @@
 - 500 Bin katılım ~ 25 Lot (2135 TL).
 - 700 Bin katılım ~ 18 Lot (1537 TL).
 - 1.1 Milyon katılım ~ 12 Lot (1024 TL).
-- 1.6 Milyon katılım ~ 6 Lot (683 TL).
-- 2.2 Milyon katılım ~ 51 Lot (512 TL).</t>
+- 1.6 Milyon katılım ~ 8 Lot (683 TL).
+- 2.2 Milyon katılım ~ 6 Lot (512 TL).</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -913,22 +913,22 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Hazırlanıyor…</t>
+          <t>18 Ağustos 2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>555.169</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%40</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>556.728</t>
         </is>
       </c>
     </row>

--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -522,12 +522,13 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>İntetra Teknoloji ve Bilişim Hizmetleri A.Ş.ı</t>
+          <t>(INTET) İntetra Teknoloji ve Bilişim Hizmetleri A.Ş.ı</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Hazırlanıyor...</t>
+          <t>26-27 Ağustos 2026
+ 10:30-13:00</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -557,14 +558,13 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>- 30 gün.</t>
+          <t>- 30 gün. * Brüt halka arz gelirinin %20'si.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>- %30 İşletme sermayesi.
-- %10 Finansal borçların ödenmesi.
-- %60 Yatırımların finansmanı.</t>
+          <t>- %35 İşletme sermayesi.
+- %65 Yatırımların finansmanı.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -574,14 +574,21 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
+          <t>- 150 Bin katılım ~ 266 Lot (14257 TL).
+- 250 Bin katılım ~ 160 Lot (8576 TL).
+- 350 Bin katılım ~ 114 Lot (6110 TL).
+- 500 Bin katılım ~ 80 Lot (4288 TL).
+- 700 Bin katılım ~ 57 Lot (3055 TL).
+- 1.1 Milyon katılım ~ 36 Lot (1929 TL).
+- 1.6 Milyon katılım ~ 25 Lot (1340 TL).
+- 2.2 Milyon katılım ~ 18 Lot (964 TL).</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Finansal Tablo - 2024/9 - 2023 - 2022
-- Hasılat - 737,6 Milyon TL - 1,7 Milyar TL - 823,4 Milyon TL
-- Brüt Kâr - 301,5 Milyon TL - 714,6 Milyon TL - 219,3 Milyon TL</t>
+          <t>Finansal Tablo - 2026/3 - 2025 - 2024
+- Hasılat - 629,0 Milyon TL - 2,5 Milyar TL - 1,7 Milyar TL
+- Brüt Kâr - 183,8 Milyon TL - 793,9 Milyon TL - 653,8 Milyon TL</t>
         </is>
       </c>
     </row>
@@ -659,60 +666,126 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>İntetra Teknoloji ve Bilişim Hizmetleri A.Ş.ı</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hazırlanıyor...</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>53,60 TL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40.000.000 Lot</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Eşit Dağıtım</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>- %25.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>～ 2,1 Milyar TL.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>- 30 gün.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>- %30 İşletme sermayesi.
+- %10 Finansal borçların ödenmesi.
+- %60 Yatırımların finansmanı.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>- Yoktur.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Finansal Tablo - 2024/9 - 2023 - 2022
+- Hasılat - 737,6 Milyon TL - 1,7 Milyar TL - 823,4 Milyon TL
+- Brüt Kâr - 301,5 Milyon TL - 714,6 Milyon TL - 219,3 Milyon TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Halka Arzı Ertelenen Şirketler</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -595,46 +595,121 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>(BKGRY) Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>24-25-26 Ağustos 2026
+ 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>12,93 TL</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>167.000.000 Lot</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Eşit Dağıtım</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>- %25.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>～ 2,1 Milyar TL.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>- 30 gün. * Brüt halka arz gelirinin %15'i.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>- %100-90 Projelerin finansmanı.
+- %0-10 İşletme sermayesi ve borç geri ödemesi.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>- 116.900.000 Lot (%70) Yurt İçi Bireysel Yatırımcı
+- 16.700.000 Lot (%10) Yüksek Başvurulu Yatırımcı
+- 33.400.000 Lot (%20) Yurt İçi Kurumsal Yatırımcı</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>- 150 Bin katılım ~ 779 Lot (10072 TL).
+- 250 Bin katılım ~ 467 Lot (6038 TL).
+- 350 Bin katılım ~ 334 Lot (4318 TL).
+- 500 Bin katılım ~ 233 Lot (3012 TL).
+- 700 Bin katılım ~ 167 Lot (2159 TL).
+- 1.1 Milyon katılım ~ 106 Lot (1370 TL).
+- 1.6 Milyon katılım ~ 73 Lot (943 TL).
+- 2.2 Milyon katılım ~ 53 Lot (685 TL).</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Finansal Tablo - 2026/3 - 2025 - 2024
+- Hasılat - 31,8 Milyon TL - 231,0 Milyon TL - 18,0 Milyon TL
+- Brüt Kâr - 24,6 Milyon TL - 111,0 Milyon TL - 18,0 Milyon TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>12,93 TL</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>167.000.000 Lot</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>- *** gün.
 (Alnus Yatırım Menkul Değerler A.Ş.)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>- %50-55 Bakırcı Ömerli lojistik merkezi projesi.
 - %15-20 Bakırcı Topkapı 2 projesi.
@@ -643,19 +718,19 @@
 - %5 Borç geri ödemesi.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>- *** Lot (%***) Yurt İçi Bireysel Yatırımcı
 - *** Lot (%***) Yüksek Başvurulu Yatırımcı
 - *** Lot (%***) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024 - 2023 - 2022
 - Hasılat - 12,5 Milyon TL - 1,5 Milyon TL - -
@@ -663,65 +738,65 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>İntetra Teknoloji ve Bilişim Hizmetleri A.Ş.ı</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>53,60 TL</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>40.000.000 Lot</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>- 30 gün.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>- %30 İşletme sermayesi.
 - %10 Finansal borçların ödenmesi.
 - %60 Yatırımların finansmanı.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>- Yoktur.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024/9 - 2023 - 2022
 - Hasılat - 737,6 Milyon TL - 1,7 Milyar TL - 823,4 Milyon TL
@@ -729,63 +804,63 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Halka Arzı Ertelenen Şirketler</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>(BKGRY) Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
+          <t>(BKRGY) Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -670,46 +670,121 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>(BKGRY) Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>24-25-26 Ağustos 2026
+ 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12,93 TL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>167.000.000 Lot</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Eşit Dağıtım</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>- %25.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>～ 2,1 Milyar TL.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>- 30 gün. * Brüt halka arz gelirinin %15'i.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>- %100-90 Projelerin finansmanı.
+- %0-10 İşletme sermayesi ve borç geri ödemesi.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>- 116.900.000 Lot (%70) Yurt İçi Bireysel Yatırımcı
+- 16.700.000 Lot (%10) Yüksek Başvurulu Yatırımcı
+- 33.400.000 Lot (%20) Yurt İçi Kurumsal Yatırımcı</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>- 150 Bin katılım ~ 779 Lot (10072 TL).
+- 250 Bin katılım ~ 467 Lot (6038 TL).
+- 350 Bin katılım ~ 334 Lot (4318 TL).
+- 500 Bin katılım ~ 233 Lot (3012 TL).
+- 700 Bin katılım ~ 167 Lot (2159 TL).
+- 1.1 Milyon katılım ~ 106 Lot (1370 TL).
+- 1.6 Milyon katılım ~ 73 Lot (943 TL).
+- 2.2 Milyon katılım ~ 53 Lot (685 TL).</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Finansal Tablo - 2026/3 - 2025 - 2024
+- Hasılat - 31,8 Milyon TL - 231,0 Milyon TL - 18,0 Milyon TL
+- Brüt Kâr - 24,6 Milyon TL - 111,0 Milyon TL - 18,0 Milyon TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>12,93 TL</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>167.000.000 Lot</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>- *** gün.
 (Alnus Yatırım Menkul Değerler A.Ş.)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>- %50-55 Bakırcı Ömerli lojistik merkezi projesi.
 - %15-20 Bakırcı Topkapı 2 projesi.
@@ -718,19 +793,19 @@
 - %5 Borç geri ödemesi.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>- *** Lot (%***) Yurt İçi Bireysel Yatırımcı
 - *** Lot (%***) Yüksek Başvurulu Yatırımcı
 - *** Lot (%***) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024 - 2023 - 2022
 - Hasılat - 12,5 Milyon TL - 1,5 Milyon TL - -
@@ -738,65 +813,65 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>İntetra Teknoloji ve Bilişim Hizmetleri A.Ş.ı</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>53,60 TL</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>40.000.000 Lot</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>- 30 gün.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>- %30 İşletme sermayesi.
 - %10 Finansal borçların ödenmesi.
 - %60 Yatırımların finansmanı.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>- Yoktur.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024/9 - 2023 - 2022
 - Hasılat - 737,6 Milyon TL - 1,7 Milyar TL - 823,4 Milyon TL
@@ -804,63 +879,63 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Halka Arzı Ertelenen Şirketler</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -898,17 +898,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>651.837</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%99,76</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>653.433</t>
         </is>
       </c>
     </row>

--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Hazırlanıyor…</t>
+          <t>1 Eylül 2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Hazırlanıyor...</t>
+          <t>2 Eylül 2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">

--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -522,59 +522,128 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Net Global Endüstriyel Yatırımlar A.Ş.ı</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Hazırlanıyor...</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>25,52 TL</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>87.500.000 Lot</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Eşit Dağıtım</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>- %28.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>～ 2,2 Milyar TL.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>- %20-30 Mevcut yatırımlara ilişkin kapasite artışları, çatı GES (Güneş Enerjisi Santrali) kurulumu ve koruge boru makine alımı.
+- %20-30 Vagon fabrikası inşaatının tamamlanması ve makine ekipmanı.
+- %20-30 Banka kredilerinin azaltılması.
+- %20-30 İşletme sermayesi.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>- *** Lot (%***) Yurt İçi Bireysel Yatırımcı
+- *** Lot (%***) Yüksek Başvurulu Yatırımcı
+- *** Lot (%***) Yurt İçi Kurumsal Yatırımcı</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Finansal Tablo - 2024 - 2023 - 2022
+- Hasılat - 1,3 Milyar TL - 2,1 Milyar TL - 1,6 Milyar TL
+- Brüt Kâr - 416,0 Milyon TL - 398,9 Milyon TL - 380,7 Milyon TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>(BKGRY) Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>24-25-26 Ağustos 2026
  09:00-17:00</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>12,93 TL</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>167.000.000 Lot</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>- 30 gün. * Brüt halka arz gelirinin %15'i.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>- %100-90 Projelerin finansmanı.
 - %0-10 İşletme sermayesi ve borç geri ödemesi.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>- 116.900.000 Lot (%70) Yurt İçi Bireysel Yatırımcı
 - 16.700.000 Lot (%10) Yüksek Başvurulu Yatırımcı
 - 33.400.000 Lot (%20) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>- 150 Bin katılım ~ 779 Lot (10072 TL).
 - 250 Bin katılım ~ 467 Lot (6038 TL).
@@ -586,7 +655,7 @@
 - 2.2 Milyon katılım ~ 53 Lot (685 TL).</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2026/3 - 2025 - 2024
 - Hasılat - 31,8 Milyon TL - 231,0 Milyon TL - 18,0 Milyon TL
@@ -594,49 +663,49 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>12,93 TL</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>167.000.000 Lot</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>- *** gün.
 (Alnus Yatırım Menkul Değerler A.Ş.)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>- %50-55 Bakırcı Ömerli lojistik merkezi projesi.
 - %15-20 Bakırcı Topkapı 2 projesi.
@@ -645,19 +714,19 @@
 - %5 Borç geri ödemesi.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>- *** Lot (%***) Yurt İçi Bireysel Yatırımcı
 - *** Lot (%***) Yüksek Başvurulu Yatırımcı
 - *** Lot (%***) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024 - 2023 - 2022
 - Hasılat - 12,5 Milyon TL - 1,5 Milyon TL - -
@@ -665,65 +734,65 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>İntetra Teknoloji ve Bilişim Hizmetleri A.Ş.ı</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>53,60 TL</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>40.000.000 Lot</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>- 30 gün.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>- %30 İşletme sermayesi.
 - %10 Finansal borçların ödenmesi.
 - %60 Yatırımların finansmanı.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>- Yoktur.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024/9 - 2023 - 2022
 - Hasılat - 737,6 Milyon TL - 1,7 Milyar TL - 823,4 Milyon TL
@@ -731,63 +800,63 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Halka Arzı Ertelenen Şirketler</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -522,45 +522,122 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>(NETGL) Net Global Endüstriyel Yatırımlar A.Ş.ı</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>9-10-11 Eylül 2026
+ 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>25,52 TL</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>87.500.000 Lot</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Eşit Dağıtım</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>- %28.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>～ 2,2 Milyar TL.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>- 15 gün.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>- %15-25 Mevcut yatırımlara ilişkin kapasite artışları, koruge boru makine alımı.
+- %20-30 Vagon fabrikası inşaatının tamamlanması ve makine ekipmanı.
+- %20-30 Banka kredilerinin azaltılması.
+- %25-35 İşletme sermayesi.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>- 35.000.000 Lot (%40) Yurt İçi Bireysel Yatırımcı
+- 30.625.000 Lot (%35) Yurt İçi Kurumsal Yatırımcı
+- 21.875.000 Lot (%25) Yurt Dışı Kurumsal Yatırımcı</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>- 150 Bin katılım ~ 233 Lot (5946 TL).
+- 250 Bin katılım ~ 140 Lot (3572 TL).
+- 350 Bin katılım ~ 100 Lot (2552 TL).
+- 500 Bin katılım ~ 70 Lot (1786 TL).
+- 700 Bin katılım ~ 50 Lot (1276 TL).
+- 1.1 Milyon katılım ~ 32 Lot (816 TL).
+- 1.6 Milyon katılım ~ 22 Lot (561 TL).
+- 2.2 Milyon katılım ~ 16 Lot (408 TL).</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Finansal Tablo - 2026/6 - 2025 - 2024
+- Hasılat - 1,0 Milyar TL - 2,1 Milyar TL - 2,0 Milyar TL
+- Brüt Kâr - 234,0 Milyon TL - 618,7 Milyon TL - 641,2 Milyon TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Net Global Endüstriyel Yatırımlar A.Ş.ı</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>25,52 TL</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>87.500.000 Lot</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>- %28.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>～ 2,2 Milyar TL.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>- %20-30 Mevcut yatırımlara ilişkin kapasite artışları, çatı GES (Güneş Enerjisi Santrali) kurulumu ve koruge boru makine alımı.
 - %20-30 Vagon fabrikası inşaatının tamamlanması ve makine ekipmanı.
@@ -568,19 +645,19 @@
 - %20-30 İşletme sermayesi.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>- *** Lot (%***) Yurt İçi Bireysel Yatırımcı
 - *** Lot (%***) Yüksek Başvurulu Yatırımcı
 - *** Lot (%***) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024 - 2023 - 2022
 - Hasılat - 1,3 Milyar TL - 2,1 Milyar TL - 1,6 Milyar TL
@@ -588,62 +665,62 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>(BKGRY) Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>24-25-26 Ağustos 2026
  09:00-17:00</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>12,93 TL</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>167.000.000 Lot</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>- 30 gün. * Brüt halka arz gelirinin %15'i.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>- %100-90 Projelerin finansmanı.
 - %0-10 İşletme sermayesi ve borç geri ödemesi.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>- 116.900.000 Lot (%70) Yurt İçi Bireysel Yatırımcı
 - 16.700.000 Lot (%10) Yüksek Başvurulu Yatırımcı
 - 33.400.000 Lot (%20) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>- 150 Bin katılım ~ 779 Lot (10072 TL).
 - 250 Bin katılım ~ 467 Lot (6038 TL).
@@ -655,7 +732,7 @@
 - 2.2 Milyon katılım ~ 53 Lot (685 TL).</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2026/3 - 2025 - 2024
 - Hasılat - 31,8 Milyon TL - 231,0 Milyon TL - 18,0 Milyon TL
@@ -663,49 +740,49 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>12,93 TL</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>167.000.000 Lot</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>- *** gün.
 (Alnus Yatırım Menkul Değerler A.Ş.)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>- %50-55 Bakırcı Ömerli lojistik merkezi projesi.
 - %15-20 Bakırcı Topkapı 2 projesi.
@@ -714,19 +791,19 @@
 - %5 Borç geri ödemesi.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>- *** Lot (%***) Yurt İçi Bireysel Yatırımcı
 - *** Lot (%***) Yüksek Başvurulu Yatırımcı
 - *** Lot (%***) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024 - 2023 - 2022
 - Hasılat - 12,5 Milyon TL - 1,5 Milyon TL - -
@@ -734,65 +811,65 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>İntetra Teknoloji ve Bilişim Hizmetleri A.Ş.ı</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>53,60 TL</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>40.000.000 Lot</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>- 30 gün.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>- %30 İşletme sermayesi.
 - %10 Finansal borçların ödenmesi.
 - %60 Yatırımların finansmanı.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>- Yoktur.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024/9 - 2023 - 2022
 - Hasılat - 737,6 Milyon TL - 1,7 Milyar TL - 823,4 Milyon TL
@@ -800,63 +877,63 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Halka Arzı Ertelenen Şirketler</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -522,7 +522,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(NETGL) Net Global Endüstriyel Yatırımlar A.Ş.ı</t>
+          <t>(NETGL) Net Global Endüstriyel Yatırımlar A.Ş.ı Talep Toplanıyor</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -599,45 +599,122 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>(NETGL) Net Global Endüstriyel Yatırımlar A.Ş.ı</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>9-10-11 Eylül 2026
+ 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>25,52 TL</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>87.500.000 Lot</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Eşit Dağıtım</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>- %28.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>～ 2,2 Milyar TL.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>- 15 gün.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>- %15-25 Mevcut yatırımlara ilişkin kapasite artışları, koruge boru makine alımı.
+- %20-30 Vagon fabrikası inşaatının tamamlanması ve makine ekipmanı.
+- %20-30 Banka kredilerinin azaltılması.
+- %25-35 İşletme sermayesi.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>- 35.000.000 Lot (%40) Yurt İçi Bireysel Yatırımcı
+- 30.625.000 Lot (%35) Yurt İçi Kurumsal Yatırımcı
+- 21.875.000 Lot (%25) Yurt Dışı Kurumsal Yatırımcı</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>- 150 Bin katılım ~ 233 Lot (5946 TL).
+- 250 Bin katılım ~ 140 Lot (3572 TL).
+- 350 Bin katılım ~ 100 Lot (2552 TL).
+- 500 Bin katılım ~ 70 Lot (1786 TL).
+- 700 Bin katılım ~ 50 Lot (1276 TL).
+- 1.1 Milyon katılım ~ 32 Lot (816 TL).
+- 1.6 Milyon katılım ~ 22 Lot (561 TL).
+- 2.2 Milyon katılım ~ 16 Lot (408 TL).</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Finansal Tablo - 2026/6 - 2025 - 2024
+- Hasılat - 1,0 Milyar TL - 2,1 Milyar TL - 2,0 Milyar TL
+- Brüt Kâr - 234,0 Milyon TL - 618,7 Milyon TL - 641,2 Milyon TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>Net Global Endüstriyel Yatırımlar A.Ş.ı</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>25,52 TL</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>87.500.000 Lot</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>- %28.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>～ 2,2 Milyar TL.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>- %20-30 Mevcut yatırımlara ilişkin kapasite artışları, çatı GES (Güneş Enerjisi Santrali) kurulumu ve koruge boru makine alımı.
 - %20-30 Vagon fabrikası inşaatının tamamlanması ve makine ekipmanı.
@@ -645,19 +722,19 @@
 - %20-30 İşletme sermayesi.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>- *** Lot (%***) Yurt İçi Bireysel Yatırımcı
 - *** Lot (%***) Yüksek Başvurulu Yatırımcı
 - *** Lot (%***) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024 - 2023 - 2022
 - Hasılat - 1,3 Milyar TL - 2,1 Milyar TL - 1,6 Milyar TL
@@ -665,62 +742,62 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>(BKGRY) Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>24-25-26 Ağustos 2026
  09:00-17:00</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>12,93 TL</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>167.000.000 Lot</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>- 30 gün. * Brüt halka arz gelirinin %15'i.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>- %100-90 Projelerin finansmanı.
 - %0-10 İşletme sermayesi ve borç geri ödemesi.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>- 116.900.000 Lot (%70) Yurt İçi Bireysel Yatırımcı
 - 16.700.000 Lot (%10) Yüksek Başvurulu Yatırımcı
 - 33.400.000 Lot (%20) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>- 150 Bin katılım ~ 779 Lot (10072 TL).
 - 250 Bin katılım ~ 467 Lot (6038 TL).
@@ -732,7 +809,7 @@
 - 2.2 Milyon katılım ~ 53 Lot (685 TL).</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2026/3 - 2025 - 2024
 - Hasılat - 31,8 Milyon TL - 231,0 Milyon TL - 18,0 Milyon TL
@@ -740,49 +817,49 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Bakırcı Gayrimenkul Yatırım Ortaklığı A.Ş.ı</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>12,93 TL</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>167.000.000 Lot</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>- *** gün.
 (Alnus Yatırım Menkul Değerler A.Ş.)</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>- %50-55 Bakırcı Ömerli lojistik merkezi projesi.
 - %15-20 Bakırcı Topkapı 2 projesi.
@@ -791,19 +868,19 @@
 - %5 Borç geri ödemesi.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>- *** Lot (%***) Yurt İçi Bireysel Yatırımcı
 - *** Lot (%***) Yüksek Başvurulu Yatırımcı
 - *** Lot (%***) Yurt İçi Kurumsal Yatırımcı</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024 - 2023 - 2022
 - Hasılat - 12,5 Milyon TL - 1,5 Milyon TL - -
@@ -811,65 +888,65 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>İntetra Teknoloji ve Bilişim Hizmetleri A.Ş.ı</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Hazırlanıyor...</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>53,60 TL</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>40.000.000 Lot</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Eşit Dağıtım</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>- %25.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>～ 2,1 Milyar TL.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>- 30 gün.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>- %30 İşletme sermayesi.
 - %10 Finansal borçların ödenmesi.
 - %60 Yatırımların finansmanı.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>- Yoktur.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>- İlerleyen aşamalarda tamamlanacaktır.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Finansal Tablo - 2024/9 - 2023 - 2022
 - Hasılat - 737,6 Milyon TL - 1,7 Milyar TL - 823,4 Milyon TL
@@ -877,63 +954,63 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Halka Arzı Ertelenen Şirketler</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
